--- a/Logboeken/Logboek Eddie.xlsx
+++ b/Logboeken/Logboek Eddie.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="22202"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="22220"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="-440" windowWidth="33600" windowHeight="21000" tabRatio="500"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
   <si>
     <t>Datum</t>
   </si>
@@ -61,6 +61,24 @@
   </si>
   <si>
     <t>Titanium Studio leren</t>
+  </si>
+  <si>
+    <t>Voorbereiding voor gesprek met opdrachtgever maken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapport maken voor de presentatie </t>
+  </si>
+  <si>
+    <t>1,5 uur</t>
+  </si>
+  <si>
+    <t>Gesprek met opdrachtgever</t>
+  </si>
+  <si>
+    <t>Presentatie van ons rapport</t>
+  </si>
+  <si>
+    <t>Begin gemaakt met de app: De kaart</t>
   </si>
 </sst>
 </file>
@@ -124,10 +142,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normaal" xfId="0" builtinId="0"/>
@@ -467,8 +485,8 @@
     <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="5" customFormat="1" ht="45">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:3" s="6" customFormat="1" ht="45">
+      <c r="A1" s="6" t="s">
         <v>6</v>
       </c>
     </row>
@@ -479,7 +497,7 @@
       <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>7</v>
       </c>
     </row>
@@ -575,30 +593,72 @@
       <c r="A11" s="3">
         <v>41023</v>
       </c>
-      <c r="B11" s="4"/>
+      <c r="B11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
+      <c r="A12" s="3">
+        <v>41024</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
+      <c r="A13" s="3">
+        <v>41024</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
+      <c r="A14" s="3">
+        <v>41025</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
+      <c r="A15" s="3">
+        <v>41025</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
+      <c r="A16" s="3">
+        <v>41026</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="4"/>
+      <c r="A17" s="3">
+        <v>41035</v>
+      </c>
       <c r="B17" s="4"/>
     </row>
     <row r="18" spans="1:2">

--- a/Logboeken/Logboek Eddie.xlsx
+++ b/Logboeken/Logboek Eddie.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="22220"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="-440" windowWidth="33600" windowHeight="21000" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="-435" windowWidth="20730" windowHeight="11760" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="140000" concurrentCalc="0"/>
+  <calcPr calcId="140000"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
@@ -75,10 +75,10 @@
     <t>Gesprek met opdrachtgever</t>
   </si>
   <si>
-    <t>Presentatie van ons rapport</t>
-  </si>
-  <si>
     <t>Begin gemaakt met de app: De kaart</t>
+  </si>
+  <si>
+    <t>Presentatie van onze definitiestudie</t>
   </si>
 </sst>
 </file>
@@ -148,10 +148,15 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normaal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -478,19 +483,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C55"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="106.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="106.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="6" customFormat="1" ht="45">
+    <row r="1" spans="1:3" s="6" customFormat="1" ht="46.5" x14ac:dyDescent="0.7">
       <c r="A1" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="23">
+    <row r="2" spans="1:3" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -501,7 +506,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>41016</v>
       </c>
@@ -512,7 +517,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>41016</v>
       </c>
@@ -523,7 +528,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>41017</v>
       </c>
@@ -534,7 +539,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>41018</v>
       </c>
@@ -545,7 +550,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>41018</v>
       </c>
@@ -556,7 +561,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>41019</v>
       </c>
@@ -567,7 +572,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>41022</v>
       </c>
@@ -578,7 +583,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>41023</v>
       </c>
@@ -589,7 +594,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>41023</v>
       </c>
@@ -600,7 +605,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>41024</v>
       </c>
@@ -611,7 +616,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>41024</v>
       </c>
@@ -622,7 +627,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>41025</v>
       </c>
@@ -633,183 +638,183 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>41025</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>41026</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>41035</v>
       </c>
       <c r="B17" s="4"/>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
     </row>
   </sheetData>

--- a/Logboeken/Logboek Eddie.xlsx
+++ b/Logboeken/Logboek Eddie.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="22220"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="-435" windowWidth="20730" windowHeight="11760" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="-440" windowWidth="33600" windowHeight="21000" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="140000"/>
+  <calcPr calcId="140000" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
   <si>
     <t>Datum</t>
   </si>
@@ -69,16 +69,37 @@
     <t xml:space="preserve">Rapport maken voor de presentatie </t>
   </si>
   <si>
+    <t>4 uur</t>
+  </si>
+  <si>
     <t>1,5 uur</t>
   </si>
   <si>
     <t>Gesprek met opdrachtgever</t>
   </si>
   <si>
+    <t>Presentatie van ons rapport</t>
+  </si>
+  <si>
     <t>Begin gemaakt met de app: De kaart</t>
   </si>
   <si>
-    <t>Presentatie van onze definitiestudie</t>
+    <t>De kaart van de app gemaakt en de verschillende kaarttypes aangemaakt</t>
+  </si>
+  <si>
+    <t>Gesprek met tutor</t>
+  </si>
+  <si>
+    <t>De map geoptimaleerd + de verschillende kaarttypes</t>
+  </si>
+  <si>
+    <t>6,5 uur</t>
+  </si>
+  <si>
+    <t>Settingspagina + searhbar bijgewerkt</t>
+  </si>
+  <si>
+    <t>5 uur</t>
   </si>
 </sst>
 </file>
@@ -148,15 +169,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normaal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -483,19 +499,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C55"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="106.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="106.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="6" customFormat="1" ht="46.5" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:3" s="6" customFormat="1" ht="45">
       <c r="A1" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="23">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -506,7 +522,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" s="3">
         <v>41016</v>
       </c>
@@ -517,7 +533,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="3">
         <v>41016</v>
       </c>
@@ -528,7 +544,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="3">
         <v>41017</v>
       </c>
@@ -539,7 +555,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" s="3">
         <v>41018</v>
       </c>
@@ -550,7 +566,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" s="3">
         <v>41018</v>
       </c>
@@ -561,7 +577,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" s="3">
         <v>41019</v>
       </c>
@@ -572,7 +588,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" s="3">
         <v>41022</v>
       </c>
@@ -583,7 +599,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" s="3">
         <v>41023</v>
       </c>
@@ -594,7 +610,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" s="3">
         <v>41023</v>
       </c>
@@ -605,7 +621,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" s="3">
         <v>41024</v>
       </c>
@@ -616,7 +632,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" s="3">
         <v>41024</v>
       </c>
@@ -624,21 +640,21 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" s="3">
         <v>41025</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" s="3">
         <v>41025</v>
       </c>
@@ -646,175 +662,203 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="3">
         <v>41026</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" s="3">
-        <v>41035</v>
-      </c>
-      <c r="B17" s="4"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
+        <v>41036</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="3">
+        <v>41037</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="3">
+        <v>41037</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="3">
+        <v>41038</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="3">
+        <v>41039</v>
+      </c>
       <c r="B21" s="4"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2">
       <c r="A55" s="4"/>
     </row>
   </sheetData>

--- a/Logboeken/Logboek Eddie.xlsx
+++ b/Logboeken/Logboek Eddie.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="30">
   <si>
     <t>Datum</t>
   </si>
@@ -100,6 +100,15 @@
   </si>
   <si>
     <t>5 uur</t>
+  </si>
+  <si>
+    <t>Bugs fixen + annotations op de kaart met icoontjes + Map optimaliseren</t>
+  </si>
+  <si>
+    <t>6 uur</t>
+  </si>
+  <si>
+    <t>Gesprek met de Opdrachtgever</t>
   </si>
 </sst>
 </file>
@@ -724,11 +733,20 @@
       <c r="A21" s="3">
         <v>41039</v>
       </c>
-      <c r="B21" s="4"/>
+      <c r="B21" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
+      <c r="A22" s="3">
+        <v>41040</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="4"/>

--- a/Logboeken/Logboek Eddie.xlsx
+++ b/Logboeken/Logboek Eddie.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="22220"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="22221"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="-440" windowWidth="33600" windowHeight="21000" tabRatio="500"/>
+    <workbookView xWindow="6760" yWindow="2120" windowWidth="25600" windowHeight="16060" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="32">
   <si>
     <t>Datum</t>
   </si>
@@ -87,9 +87,6 @@
     <t>De kaart van de app gemaakt en de verschillende kaarttypes aangemaakt</t>
   </si>
   <si>
-    <t>Gesprek met tutor</t>
-  </si>
-  <si>
     <t>De map geoptimaleerd + de verschillende kaarttypes</t>
   </si>
   <si>
@@ -109,6 +106,15 @@
   </si>
   <si>
     <t>Gesprek met de Opdrachtgever</t>
+  </si>
+  <si>
+    <t>Bugs fixen + annotations verbeterd</t>
+  </si>
+  <si>
+    <t>Trail gemaakt op de kaart + Bugs fixen</t>
+  </si>
+  <si>
+    <t>De App optimaliseren</t>
   </si>
 </sst>
 </file>
@@ -701,7 +707,7 @@
         <v>41037</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C18" t="s">
         <v>8</v>
@@ -712,10 +718,10 @@
         <v>41037</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" t="s">
         <v>23</v>
-      </c>
-      <c r="C19" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -723,10 +729,10 @@
         <v>41038</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" t="s">
         <v>25</v>
-      </c>
-      <c r="C20" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -734,10 +740,10 @@
         <v>41039</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" t="s">
         <v>27</v>
-      </c>
-      <c r="C21" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -745,31 +751,71 @@
         <v>41040</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3">
+        <v>41043</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3">
+        <v>41043</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
+      <c r="C24" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
+      <c r="A25" s="3">
+        <v>41044</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
+      <c r="A26" s="3">
+        <v>41044</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
+      <c r="A27" s="3">
+        <v>41045</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="4"/>
+      <c r="A28" s="3">
+        <v>41050</v>
+      </c>
       <c r="B28" s="4"/>
     </row>
     <row r="29" spans="1:3">

--- a/Logboeken/Logboek Eddie.xlsx
+++ b/Logboeken/Logboek Eddie.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="34">
   <si>
     <t>Datum</t>
   </si>
@@ -115,6 +115,12 @@
   </si>
   <si>
     <t>De App optimaliseren</t>
+  </si>
+  <si>
+    <t>Begin gemaakt met het rapport</t>
+  </si>
+  <si>
+    <t>Verder gewerkt aan het rapport</t>
   </si>
 </sst>
 </file>
@@ -816,23 +822,56 @@
       <c r="A28" s="3">
         <v>41050</v>
       </c>
-      <c r="B28" s="4"/>
+      <c r="B28" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
+      <c r="A29" s="3">
+        <v>41050</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
+      <c r="A30" s="3">
+        <v>41051</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
+      <c r="A31" s="3">
+        <v>41051</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
+      <c r="A32" s="3">
+        <v>41052</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="4"/>

--- a/Logboeken/Logboek Eddie.xlsx
+++ b/Logboeken/Logboek Eddie.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="39">
   <si>
     <t>Datum</t>
   </si>
@@ -121,6 +121,21 @@
   </si>
   <si>
     <t>Verder gewerkt aan het rapport</t>
+  </si>
+  <si>
+    <t>Bugs fixen</t>
+  </si>
+  <si>
+    <t>4,5 uur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deelrapport gemaakt </t>
+  </si>
+  <si>
+    <t>Searchbar op de map verwijderd + settings voor iPhone verbeterd</t>
+  </si>
+  <si>
+    <t>2 uur</t>
   </si>
 </sst>
 </file>
@@ -873,67 +888,95 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-    </row>
-    <row r="37" spans="1:2">
+    <row r="33" spans="1:3">
+      <c r="A33" s="3">
+        <v>41053</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="3">
+        <v>41054</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="3">
+        <v>41058</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="3">
+        <v>41058</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:3">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:3">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:3">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:3">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:3">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:3">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:3">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:3">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:3">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:3">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:3">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
     </row>

--- a/Logboeken/Logboek Eddie.xlsx
+++ b/Logboeken/Logboek Eddie.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="22221"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="6760" yWindow="2120" windowWidth="25600" windowHeight="16060" tabRatio="500"/>
+    <workbookView xWindow="5240" yWindow="2780" windowWidth="25600" windowHeight="16060" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="43">
   <si>
     <t>Datum</t>
   </si>
@@ -136,6 +136,18 @@
   </si>
   <si>
     <t>2 uur</t>
+  </si>
+  <si>
+    <t>Het Rapport verbeterd + Bugs fixen in de Main-App</t>
+  </si>
+  <si>
+    <t>De laatste Bugs fixen in de Main-App: op de iPhone de toon op kaart button</t>
+  </si>
+  <si>
+    <t>Visstekken app gemaakt zodat deze los staat van de Main-App</t>
+  </si>
+  <si>
+    <t>Het Rapport optimaliseren</t>
   </si>
 </sst>
 </file>
@@ -148,6 +160,7 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -933,24 +946,56 @@
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
+      <c r="A37" s="3">
+        <v>41059</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
+      <c r="A38" s="3">
+        <v>41060</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
+      <c r="A39" s="3">
+        <v>41061</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
+      <c r="A40" s="3">
+        <v>41064</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
+      <c r="A41" s="3">
+        <v>41065</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="4"/>

--- a/Logboeken/Logboek Eddie.xlsx
+++ b/Logboeken/Logboek Eddie.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="22221"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="5240" yWindow="2780" windowWidth="25600" windowHeight="16060" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="18580" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="45">
   <si>
     <t>Datum</t>
   </si>
@@ -148,6 +148,12 @@
   </si>
   <si>
     <t>Het Rapport optimaliseren</t>
+  </si>
+  <si>
+    <t>Apps klaargemaakt voor gesprek met Opdrachtgever</t>
+  </si>
+  <si>
+    <t>Rapport volledig gemaakt</t>
   </si>
 </sst>
 </file>
@@ -996,18 +1002,39 @@
       <c r="B41" s="4" t="s">
         <v>42</v>
       </c>
+      <c r="C41" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
+      <c r="A42" s="3">
+        <v>41066</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C42" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
+      <c r="A43" s="3">
+        <v>41067</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="4"/>
-      <c r="B44" s="4"/>
+      <c r="A44" s="3">
+        <v>41071</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="4"/>
